--- a/rag/evaluation/Annotations-flan-t5-large.xlsx
+++ b/rag/evaluation/Annotations-flan-t5-large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Desktop/nlp-hw1/rag/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0865F8D-4A9D-5A4C-97A5-AD0FBD7C0FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A739418-3C34-BC49-A881-4A031DDF8A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4225,8 +4225,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4532,14 +4535,17 @@
   <dimension ref="A1:I251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="54" customWidth="1"/>
+    <col min="2" max="2" width="53.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="6" width="32.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -4548,10 +4554,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -4564,11 +4570,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
@@ -4577,21 +4583,24 @@
       <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
@@ -4600,21 +4609,24 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
@@ -4623,21 +4635,24 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
@@ -4646,21 +4661,24 @@
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
@@ -4669,21 +4687,24 @@
       <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C7" t="s">
@@ -4692,21 +4713,24 @@
       <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>44</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
@@ -4715,21 +4739,24 @@
       <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
@@ -4738,21 +4765,24 @@
       <c r="D9" t="s">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C10" t="s">
@@ -4761,21 +4791,24 @@
       <c r="D10" t="s">
         <v>58</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C11" t="s">
@@ -4784,21 +4817,24 @@
       <c r="D11" t="s">
         <v>63</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>64</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C12" t="s">
@@ -4807,21 +4843,24 @@
       <c r="D12" t="s">
         <v>68</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>70</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C13" t="s">
@@ -4830,21 +4869,24 @@
       <c r="D13" t="s">
         <v>73</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>76</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C14" t="s">
@@ -4853,21 +4895,24 @@
       <c r="D14" t="s">
         <v>79</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>81</v>
       </c>
       <c r="G14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>82</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
@@ -4876,21 +4921,24 @@
       <c r="D15" t="s">
         <v>85</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>88</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C16" t="s">
@@ -4899,21 +4947,24 @@
       <c r="D16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>93</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>94</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C17" t="s">
@@ -4922,21 +4973,24 @@
       <c r="D17" t="s">
         <v>97</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>100</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C18" t="s">
@@ -4945,21 +4999,24 @@
       <c r="D18" t="s">
         <v>103</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>104</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>105</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C19" t="s">
@@ -4968,21 +5025,24 @@
       <c r="D19" t="s">
         <v>108</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>109</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>110</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C20" t="s">
@@ -4991,21 +5051,24 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>114</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>115</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C21" t="s">
@@ -5014,21 +5077,24 @@
       <c r="D21" t="s">
         <v>118</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>120</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C22" t="s">
@@ -5037,21 +5103,24 @@
       <c r="D22" t="s">
         <v>123</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>124</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>125</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C23" t="s">
@@ -5060,21 +5129,24 @@
       <c r="D23" t="s">
         <v>128</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>129</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>130</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C24" t="s">
@@ -5083,21 +5155,24 @@
       <c r="D24" t="s">
         <v>133</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G24" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>136</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C25" t="s">
@@ -5106,21 +5181,24 @@
       <c r="D25" t="s">
         <v>139</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>141</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C26" t="s">
@@ -5129,21 +5207,24 @@
       <c r="D26" t="s">
         <v>144</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>146</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C27" t="s">
@@ -5152,21 +5233,24 @@
       <c r="D27" t="s">
         <v>149</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>151</v>
       </c>
       <c r="G27" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>152</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C28" t="s">
@@ -5175,21 +5259,24 @@
       <c r="D28" t="s">
         <v>155</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>157</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>158</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C29" t="s">
@@ -5198,21 +5285,24 @@
       <c r="D29" t="s">
         <v>160</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>162</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>163</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C30" t="s">
@@ -5221,21 +5311,24 @@
       <c r="D30" t="s">
         <v>166</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>168</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>169</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C31" t="s">
@@ -5244,21 +5337,24 @@
       <c r="D31" t="s">
         <v>172</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>174</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C32" t="s">
@@ -5267,21 +5363,24 @@
       <c r="D32" t="s">
         <v>177</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>178</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>179</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C33" t="s">
@@ -5290,21 +5389,24 @@
       <c r="D33" t="s">
         <v>182</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>185</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C34" t="s">
@@ -5313,21 +5415,24 @@
       <c r="D34" t="s">
         <v>188</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>190</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>191</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>192</v>
       </c>
       <c r="C35" t="s">
@@ -5336,21 +5441,24 @@
       <c r="D35" t="s">
         <v>194</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>196</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>197</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C36" t="s">
@@ -5359,21 +5467,24 @@
       <c r="D36" t="s">
         <v>200</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>201</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>202</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>203</v>
       </c>
       <c r="C37" t="s">
@@ -5382,21 +5493,24 @@
       <c r="D37" t="s">
         <v>204</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>205</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>206</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C38" t="s">
@@ -5405,21 +5519,24 @@
       <c r="D38" t="s">
         <v>208</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>210</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>211</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C39" t="s">
@@ -5428,21 +5545,24 @@
       <c r="D39" t="s">
         <v>214</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>216</v>
       </c>
       <c r="G39" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>217</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C40" t="s">
@@ -5451,21 +5571,24 @@
       <c r="D40" t="s">
         <v>220</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>222</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>223</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>224</v>
       </c>
       <c r="C41" t="s">
@@ -5474,21 +5597,24 @@
       <c r="D41" t="s">
         <v>226</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>228</v>
       </c>
       <c r="G41" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>229</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C42" t="s">
@@ -5497,21 +5623,24 @@
       <c r="D42" t="s">
         <v>232</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>233</v>
       </c>
       <c r="G42" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>234</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C43" t="s">
@@ -5520,21 +5649,24 @@
       <c r="D43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>239</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>240</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>241</v>
       </c>
       <c r="C44" t="s">
@@ -5543,21 +5675,24 @@
       <c r="D44" t="s">
         <v>243</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>244</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>245</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>246</v>
       </c>
       <c r="C45" t="s">
@@ -5566,21 +5701,24 @@
       <c r="D45" t="s">
         <v>248</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>249</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>250</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>251</v>
       </c>
       <c r="C46" t="s">
@@ -5589,21 +5727,24 @@
       <c r="D46" t="s">
         <v>253</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>255</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>256</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>257</v>
       </c>
       <c r="C47" t="s">
@@ -5612,21 +5753,24 @@
       <c r="D47" t="s">
         <v>259</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>260</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>261</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C48" t="s">
@@ -5635,21 +5779,24 @@
       <c r="D48" t="s">
         <v>264</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>266</v>
       </c>
       <c r="G48" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>267</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>268</v>
       </c>
       <c r="C49" t="s">
@@ -5658,21 +5805,24 @@
       <c r="D49" t="s">
         <v>270</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>272</v>
       </c>
       <c r="G49" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>273</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C50" t="s">
@@ -5681,21 +5831,24 @@
       <c r="D50" t="s">
         <v>276</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>278</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>279</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>280</v>
       </c>
       <c r="C51" t="s">
@@ -5704,21 +5857,24 @@
       <c r="D51" t="s">
         <v>282</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>284</v>
       </c>
       <c r="G51" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>285</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>286</v>
       </c>
       <c r="C52" t="s">
@@ -5727,21 +5883,24 @@
       <c r="D52" t="s">
         <v>288</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>290</v>
       </c>
       <c r="G52" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>291</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C53" t="s">
@@ -5750,21 +5909,24 @@
       <c r="D53" t="s">
         <v>294</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>296</v>
       </c>
       <c r="G53" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>297</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C54" t="s">
@@ -5773,21 +5935,24 @@
       <c r="D54" t="s">
         <v>300</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>301</v>
       </c>
       <c r="G54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>302</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>303</v>
       </c>
       <c r="C55" t="s">
@@ -5796,21 +5961,24 @@
       <c r="D55" t="s">
         <v>305</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>307</v>
       </c>
       <c r="G55" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>308</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C56" t="s">
@@ -5819,21 +5987,24 @@
       <c r="D56" t="s">
         <v>311</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>313</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>314</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C57" t="s">
@@ -5842,21 +6013,24 @@
       <c r="D57" t="s">
         <v>317</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>319</v>
       </c>
       <c r="G57" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>320</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>321</v>
       </c>
       <c r="C58" t="s">
@@ -5865,21 +6039,24 @@
       <c r="D58" t="s">
         <v>323</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>324</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>325</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>326</v>
       </c>
       <c r="C59" t="s">
@@ -5888,21 +6065,24 @@
       <c r="D59" t="s">
         <v>328</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>329</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>330</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>331</v>
       </c>
       <c r="C60" t="s">
@@ -5911,21 +6091,24 @@
       <c r="D60" t="s">
         <v>333</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>334</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>335</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>336</v>
       </c>
       <c r="C61" t="s">
@@ -5934,21 +6117,24 @@
       <c r="D61" t="s">
         <v>338</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>340</v>
       </c>
       <c r="G61" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>341</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>342</v>
       </c>
       <c r="C62" t="s">
@@ -5957,21 +6143,24 @@
       <c r="D62" t="s">
         <v>344</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>346</v>
       </c>
       <c r="G62" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>347</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>348</v>
       </c>
       <c r="C63" t="s">
@@ -5980,21 +6169,24 @@
       <c r="D63" t="s">
         <v>350</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>351</v>
       </c>
       <c r="G63" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>352</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>353</v>
       </c>
       <c r="C64" t="s">
@@ -6003,21 +6195,24 @@
       <c r="D64" t="s">
         <v>355</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="1" t="s">
         <v>357</v>
       </c>
       <c r="G64" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>358</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>359</v>
       </c>
       <c r="C65" t="s">
@@ -6026,21 +6221,24 @@
       <c r="D65" t="s">
         <v>360</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="1" t="s">
         <v>362</v>
       </c>
       <c r="G65" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>363</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C66" t="s">
@@ -6049,21 +6247,24 @@
       <c r="D66" t="s">
         <v>366</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="1" t="s">
         <v>368</v>
       </c>
       <c r="G66" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>369</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>370</v>
       </c>
       <c r="C67" t="s">
@@ -6072,21 +6273,24 @@
       <c r="D67" t="s">
         <v>372</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="1" t="s">
         <v>373</v>
       </c>
       <c r="G67" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>374</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C68" t="s">
@@ -6095,21 +6299,24 @@
       <c r="D68" t="s">
         <v>376</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="1" t="s">
         <v>378</v>
       </c>
       <c r="G68" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>379</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>380</v>
       </c>
       <c r="C69" t="s">
@@ -6118,21 +6325,24 @@
       <c r="D69" t="s">
         <v>382</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="1" t="s">
         <v>384</v>
       </c>
       <c r="G69" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>385</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>386</v>
       </c>
       <c r="C70" t="s">
@@ -6141,21 +6351,24 @@
       <c r="D70" t="s">
         <v>388</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>390</v>
       </c>
       <c r="G70" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>391</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>392</v>
       </c>
       <c r="C71" t="s">
@@ -6164,21 +6377,24 @@
       <c r="D71" t="s">
         <v>394</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="1" t="s">
         <v>396</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>397</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>398</v>
       </c>
       <c r="C72" t="s">
@@ -6187,21 +6403,24 @@
       <c r="D72" t="s">
         <v>400</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>402</v>
       </c>
       <c r="G72" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>403</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>404</v>
       </c>
       <c r="C73" t="s">
@@ -6210,21 +6429,24 @@
       <c r="D73" t="s">
         <v>406</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>408</v>
       </c>
       <c r="G73" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>409</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>410</v>
       </c>
       <c r="C74" t="s">
@@ -6233,21 +6455,24 @@
       <c r="D74" t="s">
         <v>412</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>414</v>
       </c>
       <c r="G74" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>415</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>416</v>
       </c>
       <c r="C75" t="s">
@@ -6256,21 +6481,24 @@
       <c r="D75" t="s">
         <v>418</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>420</v>
       </c>
       <c r="G75" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>421</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>422</v>
       </c>
       <c r="C76" t="s">
@@ -6279,21 +6507,24 @@
       <c r="D76" t="s">
         <v>424</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>425</v>
       </c>
       <c r="G76" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>426</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C77" t="s">
@@ -6302,21 +6533,24 @@
       <c r="D77" t="s">
         <v>429</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="1" t="s">
         <v>430</v>
       </c>
       <c r="G77" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>431</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" t="s">
@@ -6325,21 +6559,24 @@
       <c r="D78" t="s">
         <v>434</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>436</v>
       </c>
       <c r="G78" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>437</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>438</v>
       </c>
       <c r="C79" t="s">
@@ -6348,21 +6585,24 @@
       <c r="D79" t="s">
         <v>440</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>442</v>
       </c>
       <c r="G79" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>443</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>444</v>
       </c>
       <c r="C80" t="s">
@@ -6371,21 +6611,24 @@
       <c r="D80" t="s">
         <v>446</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>448</v>
       </c>
       <c r="G80" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>449</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>450</v>
       </c>
       <c r="C81" t="s">
@@ -6394,21 +6637,24 @@
       <c r="D81" t="s">
         <v>452</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>453</v>
       </c>
       <c r="G81" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>454</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>455</v>
       </c>
       <c r="C82" t="s">
@@ -6417,21 +6663,24 @@
       <c r="D82" t="s">
         <v>457</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>459</v>
       </c>
       <c r="G82" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>460</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>461</v>
       </c>
       <c r="C83" t="s">
@@ -6440,21 +6689,24 @@
       <c r="D83" t="s">
         <v>463</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="1" t="s">
         <v>465</v>
       </c>
       <c r="G83" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>466</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>467</v>
       </c>
       <c r="C84" t="s">
@@ -6463,21 +6715,24 @@
       <c r="D84" t="s">
         <v>469</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="1" t="s">
         <v>471</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>472</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>473</v>
       </c>
       <c r="C85" t="s">
@@ -6486,21 +6741,24 @@
       <c r="D85" t="s">
         <v>475</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="1" t="s">
         <v>476</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>477</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>478</v>
       </c>
       <c r="C86" t="s">
@@ -6509,21 +6767,24 @@
       <c r="D86" t="s">
         <v>480</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="1" t="s">
         <v>482</v>
       </c>
       <c r="G86" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>483</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>484</v>
       </c>
       <c r="C87" t="s">
@@ -6532,21 +6793,24 @@
       <c r="D87" t="s">
         <v>486</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="1" t="s">
         <v>487</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>488</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>489</v>
       </c>
       <c r="C88" t="s">
@@ -6555,21 +6819,24 @@
       <c r="D88" t="s">
         <v>491</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="1" t="s">
         <v>493</v>
       </c>
       <c r="G88" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>494</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>495</v>
       </c>
       <c r="C89" t="s">
@@ -6578,21 +6845,24 @@
       <c r="D89" t="s">
         <v>497</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="1" t="s">
         <v>498</v>
       </c>
       <c r="G89" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>499</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>500</v>
       </c>
       <c r="C90" t="s">
@@ -6601,21 +6871,24 @@
       <c r="D90" t="s">
         <v>502</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>505</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>506</v>
       </c>
       <c r="C91" t="s">
@@ -6624,21 +6897,24 @@
       <c r="D91" t="s">
         <v>508</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="1" t="s">
         <v>510</v>
       </c>
       <c r="G91" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>511</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>512</v>
       </c>
       <c r="C92" t="s">
@@ -6647,21 +6923,24 @@
       <c r="D92" t="s">
         <v>514</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="1" t="s">
         <v>516</v>
       </c>
       <c r="G92" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>517</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>518</v>
       </c>
       <c r="C93" t="s">
@@ -6670,21 +6949,24 @@
       <c r="D93" t="s">
         <v>520</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="1" t="s">
         <v>522</v>
       </c>
       <c r="G93" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>523</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>524</v>
       </c>
       <c r="C94" t="s">
@@ -6693,21 +6975,24 @@
       <c r="D94" t="s">
         <v>526</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="1" t="s">
         <v>528</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>529</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>530</v>
       </c>
       <c r="C95" t="s">
@@ -6716,21 +7001,24 @@
       <c r="D95" t="s">
         <v>532</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="1" t="s">
         <v>534</v>
       </c>
       <c r="G95" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>535</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>536</v>
       </c>
       <c r="C96" t="s">
@@ -6739,21 +7027,24 @@
       <c r="D96" t="s">
         <v>538</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="1" t="s">
         <v>539</v>
       </c>
       <c r="G96" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>540</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>541</v>
       </c>
       <c r="C97" t="s">
@@ -6762,21 +7053,24 @@
       <c r="D97" t="s">
         <v>543</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="1" t="s">
         <v>545</v>
       </c>
       <c r="G97" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>546</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>547</v>
       </c>
       <c r="C98" t="s">
@@ -6785,21 +7079,24 @@
       <c r="D98" t="s">
         <v>549</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="1" t="s">
         <v>551</v>
       </c>
       <c r="G98" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>552</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>553</v>
       </c>
       <c r="C99" t="s">
@@ -6808,21 +7105,24 @@
       <c r="D99" t="s">
         <v>555</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="1" t="s">
         <v>557</v>
       </c>
       <c r="G99" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>558</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>559</v>
       </c>
       <c r="C100" t="s">
@@ -6831,21 +7131,24 @@
       <c r="D100" t="s">
         <v>561</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="1" t="s">
         <v>563</v>
       </c>
       <c r="G100" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>564</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>565</v>
       </c>
       <c r="C101" t="s">
@@ -6854,21 +7157,24 @@
       <c r="D101" t="s">
         <v>567</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>568</v>
       </c>
       <c r="G101" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>569</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>570</v>
       </c>
       <c r="C102" t="s">
@@ -6877,21 +7183,24 @@
       <c r="D102" t="s">
         <v>572</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="1" t="s">
         <v>574</v>
       </c>
       <c r="G102" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>575</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>576</v>
       </c>
       <c r="C103" t="s">
@@ -6900,21 +7209,24 @@
       <c r="D103" t="s">
         <v>578</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="1" t="s">
         <v>580</v>
       </c>
       <c r="G103" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>581</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>582</v>
       </c>
       <c r="C104" t="s">
@@ -6923,21 +7235,24 @@
       <c r="D104" t="s">
         <v>583</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="1" t="s">
         <v>585</v>
       </c>
       <c r="G104" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>586</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>587</v>
       </c>
       <c r="C105" t="s">
@@ -6946,21 +7261,24 @@
       <c r="D105" t="s">
         <v>588</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="1" t="s">
         <v>589</v>
       </c>
       <c r="G105" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>590</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>591</v>
       </c>
       <c r="C106" t="s">
@@ -6969,21 +7287,24 @@
       <c r="D106" t="s">
         <v>593</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="1" t="s">
         <v>595</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>596</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>597</v>
       </c>
       <c r="C107" t="s">
@@ -6992,21 +7313,24 @@
       <c r="D107" t="s">
         <v>599</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="1" t="s">
         <v>601</v>
       </c>
       <c r="G107" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>602</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>603</v>
       </c>
       <c r="C108" t="s">
@@ -7015,21 +7339,24 @@
       <c r="D108" t="s">
         <v>605</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="1" t="s">
         <v>606</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>607</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="1" t="s">
         <v>608</v>
       </c>
       <c r="C109" t="s">
@@ -7038,21 +7365,24 @@
       <c r="D109" t="s">
         <v>610</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" s="1" t="s">
         <v>612</v>
       </c>
       <c r="G109" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>613</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>614</v>
       </c>
       <c r="C110" t="s">
@@ -7061,21 +7391,24 @@
       <c r="D110" t="s">
         <v>616</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="1" t="s">
         <v>617</v>
       </c>
       <c r="G110" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>618</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>619</v>
       </c>
       <c r="C111" t="s">
@@ -7084,21 +7417,24 @@
       <c r="D111" t="s">
         <v>621</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" s="1" t="s">
         <v>622</v>
       </c>
       <c r="G111" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>623</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="1" t="s">
         <v>624</v>
       </c>
       <c r="C112" t="s">
@@ -7107,21 +7443,24 @@
       <c r="D112" t="s">
         <v>626</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="1" t="s">
         <v>628</v>
       </c>
       <c r="G112" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>629</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="1" t="s">
         <v>630</v>
       </c>
       <c r="C113" t="s">
@@ -7130,21 +7469,24 @@
       <c r="D113" t="s">
         <v>631</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="1" t="s">
         <v>632</v>
       </c>
       <c r="G113" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>633</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="1" t="s">
         <v>634</v>
       </c>
       <c r="C114" t="s">
@@ -7153,21 +7495,24 @@
       <c r="D114" t="s">
         <v>636</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="1" t="s">
         <v>637</v>
       </c>
       <c r="G114" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>638</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>639</v>
       </c>
       <c r="C115" t="s">
@@ -7176,21 +7521,24 @@
       <c r="D115" t="s">
         <v>641</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="1" t="s">
         <v>643</v>
       </c>
       <c r="G115" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>644</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>645</v>
       </c>
       <c r="C116" t="s">
@@ -7199,21 +7547,24 @@
       <c r="D116" t="s">
         <v>647</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="1" t="s">
         <v>649</v>
       </c>
       <c r="G116" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>650</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>651</v>
       </c>
       <c r="C117" t="s">
@@ -7222,21 +7573,24 @@
       <c r="D117" t="s">
         <v>653</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="1" t="s">
         <v>655</v>
       </c>
       <c r="G117" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>656</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>657</v>
       </c>
       <c r="C118" t="s">
@@ -7245,21 +7599,24 @@
       <c r="D118" t="s">
         <v>659</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="1" t="s">
         <v>661</v>
       </c>
       <c r="G118" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>662</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>663</v>
       </c>
       <c r="C119" t="s">
@@ -7268,21 +7625,24 @@
       <c r="D119" t="s">
         <v>665</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="1" t="s">
         <v>667</v>
       </c>
       <c r="G119" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>668</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>669</v>
       </c>
       <c r="C120" t="s">
@@ -7291,21 +7651,24 @@
       <c r="D120" t="s">
         <v>671</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F120" s="1" t="s">
         <v>672</v>
       </c>
       <c r="G120" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>673</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>674</v>
       </c>
       <c r="C121" t="s">
@@ -7314,21 +7677,24 @@
       <c r="D121" t="s">
         <v>676</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="1" t="s">
         <v>678</v>
       </c>
       <c r="G121" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>679</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>680</v>
       </c>
       <c r="C122" t="s">
@@ -7337,21 +7703,24 @@
       <c r="D122" t="s">
         <v>682</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="1" t="s">
         <v>683</v>
       </c>
       <c r="G122" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>684</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>685</v>
       </c>
       <c r="C123" t="s">
@@ -7360,21 +7729,24 @@
       <c r="D123" t="s">
         <v>687</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" s="1" t="s">
         <v>689</v>
       </c>
       <c r="G123" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>690</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>691</v>
       </c>
       <c r="C124" t="s">
@@ -7383,21 +7755,24 @@
       <c r="D124" t="s">
         <v>693</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="1" t="s">
         <v>695</v>
       </c>
       <c r="G124" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>696</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="1" t="s">
         <v>697</v>
       </c>
       <c r="C125" t="s">
@@ -7406,21 +7781,24 @@
       <c r="D125" t="s">
         <v>699</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="1" t="s">
         <v>701</v>
       </c>
       <c r="G125" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>702</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="1" t="s">
         <v>703</v>
       </c>
       <c r="C126" t="s">
@@ -7429,21 +7807,24 @@
       <c r="D126" t="s">
         <v>705</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" s="1" t="s">
         <v>706</v>
       </c>
       <c r="G126" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>707</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>708</v>
       </c>
       <c r="C127" t="s">
@@ -7452,21 +7833,24 @@
       <c r="D127" t="s">
         <v>710</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" s="1" t="s">
         <v>712</v>
       </c>
       <c r="G127" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>713</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>714</v>
       </c>
       <c r="C128" t="s">
@@ -7475,21 +7859,24 @@
       <c r="D128" t="s">
         <v>716</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="1" t="s">
         <v>718</v>
       </c>
       <c r="G128" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>719</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>720</v>
       </c>
       <c r="C129" t="s">
@@ -7498,21 +7885,24 @@
       <c r="D129" t="s">
         <v>721</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" s="1" t="s">
         <v>722</v>
       </c>
       <c r="G129" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>723</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="1" t="s">
         <v>724</v>
       </c>
       <c r="C130" t="s">
@@ -7521,21 +7911,24 @@
       <c r="D130" t="s">
         <v>726</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="1" t="s">
         <v>728</v>
       </c>
       <c r="G130" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>729</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>730</v>
       </c>
       <c r="C131" t="s">
@@ -7544,21 +7937,24 @@
       <c r="D131" t="s">
         <v>732</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="1" t="s">
         <v>734</v>
       </c>
       <c r="G131" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>735</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>736</v>
       </c>
       <c r="C132" t="s">
@@ -7567,21 +7963,24 @@
       <c r="D132" t="s">
         <v>738</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F132" s="1" t="s">
         <v>740</v>
       </c>
       <c r="G132" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>741</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>742</v>
       </c>
       <c r="C133" t="s">
@@ -7590,21 +7989,24 @@
       <c r="D133" t="s">
         <v>744</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="1" t="s">
         <v>746</v>
       </c>
       <c r="G133" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>747</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>748</v>
       </c>
       <c r="C134" t="s">
@@ -7613,21 +8015,24 @@
       <c r="D134" t="s">
         <v>750</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="1" t="s">
         <v>752</v>
       </c>
       <c r="G134" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>753</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>754</v>
       </c>
       <c r="C135" t="s">
@@ -7636,21 +8041,24 @@
       <c r="D135" t="s">
         <v>756</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="1" t="s">
         <v>757</v>
       </c>
       <c r="G135" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>758</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>759</v>
       </c>
       <c r="C136" t="s">
@@ -7659,21 +8067,24 @@
       <c r="D136" t="s">
         <v>761</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="1" t="s">
         <v>763</v>
       </c>
       <c r="G136" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>764</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>765</v>
       </c>
       <c r="C137" t="s">
@@ -7682,21 +8093,24 @@
       <c r="D137" t="s">
         <v>767</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="F137" t="s">
+      <c r="F137" s="1" t="s">
         <v>769</v>
       </c>
       <c r="G137" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>770</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="1" t="s">
         <v>771</v>
       </c>
       <c r="C138" t="s">
@@ -7705,21 +8119,24 @@
       <c r="D138" t="s">
         <v>773</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="1" t="s">
         <v>775</v>
       </c>
       <c r="G138" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>776</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="1" t="s">
         <v>777</v>
       </c>
       <c r="C139" t="s">
@@ -7728,21 +8145,24 @@
       <c r="D139" t="s">
         <v>779</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="1" t="s">
         <v>780</v>
       </c>
       <c r="G139" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>781</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="1" t="s">
         <v>782</v>
       </c>
       <c r="C140" t="s">
@@ -7751,21 +8171,24 @@
       <c r="D140" t="s">
         <v>784</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="F140" t="s">
+      <c r="F140" s="1" t="s">
         <v>786</v>
       </c>
       <c r="G140" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>787</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="1" t="s">
         <v>788</v>
       </c>
       <c r="C141" t="s">
@@ -7774,21 +8197,24 @@
       <c r="D141" t="s">
         <v>790</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="F141" t="s">
+      <c r="F141" s="1" t="s">
         <v>791</v>
       </c>
       <c r="G141" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>792</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C142" t="s">
@@ -7797,21 +8223,24 @@
       <c r="D142" t="s">
         <v>794</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F142" s="1" t="s">
         <v>795</v>
       </c>
       <c r="G142" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>796</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="1" t="s">
         <v>797</v>
       </c>
       <c r="C143" t="s">
@@ -7820,21 +8249,24 @@
       <c r="D143" t="s">
         <v>799</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F143" s="1" t="s">
         <v>801</v>
       </c>
       <c r="G143" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>802</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="1" t="s">
         <v>803</v>
       </c>
       <c r="C144" t="s">
@@ -7843,21 +8275,24 @@
       <c r="D144" t="s">
         <v>805</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F144" s="1" t="s">
         <v>807</v>
       </c>
       <c r="G144" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>808</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="1" t="s">
         <v>809</v>
       </c>
       <c r="C145" t="s">
@@ -7866,21 +8301,24 @@
       <c r="D145" t="s">
         <v>811</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F145" s="1" t="s">
         <v>813</v>
       </c>
       <c r="G145" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>814</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="1" t="s">
         <v>815</v>
       </c>
       <c r="C146" t="s">
@@ -7889,21 +8327,24 @@
       <c r="D146" t="s">
         <v>817</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F146" s="1" t="s">
         <v>819</v>
       </c>
       <c r="G146" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>820</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="1" t="s">
         <v>821</v>
       </c>
       <c r="C147" t="s">
@@ -7912,21 +8353,24 @@
       <c r="D147" t="s">
         <v>823</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F147" s="1" t="s">
         <v>824</v>
       </c>
       <c r="G147" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>825</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="1" t="s">
         <v>826</v>
       </c>
       <c r="C148" t="s">
@@ -7935,21 +8379,24 @@
       <c r="D148" t="s">
         <v>828</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F148" s="1" t="s">
         <v>830</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>831</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="1" t="s">
         <v>832</v>
       </c>
       <c r="C149" t="s">
@@ -7958,21 +8405,24 @@
       <c r="D149" t="s">
         <v>834</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="F149" t="s">
+      <c r="F149" s="1" t="s">
         <v>836</v>
       </c>
       <c r="G149" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>837</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="1" t="s">
         <v>838</v>
       </c>
       <c r="C150" t="s">
@@ -7981,21 +8431,24 @@
       <c r="D150" t="s">
         <v>840</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="F150" t="s">
+      <c r="F150" s="1" t="s">
         <v>842</v>
       </c>
       <c r="G150" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>843</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="1" t="s">
         <v>844</v>
       </c>
       <c r="C151" t="s">
@@ -8004,21 +8457,24 @@
       <c r="D151" t="s">
         <v>846</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="1" t="s">
         <v>848</v>
       </c>
       <c r="G151" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>849</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="1" t="s">
         <v>850</v>
       </c>
       <c r="C152" t="s">
@@ -8027,21 +8483,24 @@
       <c r="D152" t="s">
         <v>852</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F152" s="1" t="s">
         <v>854</v>
       </c>
       <c r="G152" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>855</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="1" t="s">
         <v>856</v>
       </c>
       <c r="C153" t="s">
@@ -8050,21 +8509,24 @@
       <c r="D153" t="s">
         <v>858</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="1" t="s">
         <v>859</v>
       </c>
       <c r="G153" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>860</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="1" t="s">
         <v>861</v>
       </c>
       <c r="C154" t="s">
@@ -8073,21 +8535,24 @@
       <c r="D154" t="s">
         <v>863</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F154" s="1" t="s">
         <v>865</v>
       </c>
       <c r="G154" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>866</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="1" t="s">
         <v>867</v>
       </c>
       <c r="C155" t="s">
@@ -8096,21 +8561,24 @@
       <c r="D155" t="s">
         <v>868</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="1" t="s">
         <v>870</v>
       </c>
       <c r="G155" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>871</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="1" t="s">
         <v>872</v>
       </c>
       <c r="C156" t="s">
@@ -8119,21 +8587,24 @@
       <c r="D156" t="s">
         <v>874</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F156" s="1" t="s">
         <v>876</v>
       </c>
       <c r="G156" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>877</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="1" t="s">
         <v>878</v>
       </c>
       <c r="C157" t="s">
@@ -8142,21 +8613,24 @@
       <c r="D157" t="s">
         <v>879</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F157" s="1" t="s">
         <v>880</v>
       </c>
       <c r="G157" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>881</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="1" t="s">
         <v>882</v>
       </c>
       <c r="C158" t="s">
@@ -8165,21 +8639,24 @@
       <c r="D158" t="s">
         <v>883</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F158" s="1" t="s">
         <v>885</v>
       </c>
       <c r="G158" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>886</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="1" t="s">
         <v>887</v>
       </c>
       <c r="C159" t="s">
@@ -8188,21 +8665,24 @@
       <c r="D159" t="s">
         <v>888</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="F159" t="s">
+      <c r="F159" s="1" t="s">
         <v>890</v>
       </c>
       <c r="G159" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>891</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="1" t="s">
         <v>892</v>
       </c>
       <c r="C160" t="s">
@@ -8211,21 +8691,24 @@
       <c r="D160" t="s">
         <v>894</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="F160" t="s">
+      <c r="F160" s="1" t="s">
         <v>895</v>
       </c>
       <c r="G160" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>896</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="1" t="s">
         <v>897</v>
       </c>
       <c r="C161" t="s">
@@ -8234,21 +8717,24 @@
       <c r="D161" t="s">
         <v>899</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F161" s="1" t="s">
         <v>901</v>
       </c>
       <c r="G161" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>902</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="1" t="s">
         <v>903</v>
       </c>
       <c r="C162" t="s">
@@ -8257,21 +8743,24 @@
       <c r="D162" t="s">
         <v>904</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F162" s="1" t="s">
         <v>906</v>
       </c>
       <c r="G162" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>907</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="1" t="s">
         <v>908</v>
       </c>
       <c r="C163" t="s">
@@ -8280,21 +8769,24 @@
       <c r="D163" t="s">
         <v>910</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F163" s="1" t="s">
         <v>912</v>
       </c>
       <c r="G163" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>913</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="1" t="s">
         <v>914</v>
       </c>
       <c r="C164" t="s">
@@ -8303,21 +8795,24 @@
       <c r="D164" t="s">
         <v>916</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F164" s="1" t="s">
         <v>918</v>
       </c>
       <c r="G164" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>919</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="1" t="s">
         <v>920</v>
       </c>
       <c r="C165" t="s">
@@ -8326,21 +8821,24 @@
       <c r="D165" t="s">
         <v>921</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="F165" t="s">
+      <c r="F165" s="1" t="s">
         <v>922</v>
       </c>
       <c r="G165" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>923</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="1" t="s">
         <v>924</v>
       </c>
       <c r="C166" t="s">
@@ -8349,21 +8847,24 @@
       <c r="D166" t="s">
         <v>926</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F166" s="1" t="s">
         <v>928</v>
       </c>
       <c r="G166" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>929</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="1" t="s">
         <v>930</v>
       </c>
       <c r="C167" t="s">
@@ -8372,21 +8873,24 @@
       <c r="D167" t="s">
         <v>932</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="F167" t="s">
+      <c r="F167" s="1" t="s">
         <v>934</v>
       </c>
       <c r="G167" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>935</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="1" t="s">
         <v>936</v>
       </c>
       <c r="C168" t="s">
@@ -8395,21 +8899,24 @@
       <c r="D168" t="s">
         <v>938</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F168" s="1" t="s">
         <v>940</v>
       </c>
       <c r="G168" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>941</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="1" t="s">
         <v>942</v>
       </c>
       <c r="C169" t="s">
@@ -8418,21 +8925,24 @@
       <c r="D169" t="s">
         <v>944</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F169" s="1" t="s">
         <v>946</v>
       </c>
       <c r="G169" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>947</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="1" t="s">
         <v>948</v>
       </c>
       <c r="C170" t="s">
@@ -8441,21 +8951,24 @@
       <c r="D170" t="s">
         <v>950</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E170" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F170" s="1" t="s">
         <v>951</v>
       </c>
       <c r="G170" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>952</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="1" t="s">
         <v>953</v>
       </c>
       <c r="C171" t="s">
@@ -8464,21 +8977,24 @@
       <c r="D171" t="s">
         <v>955</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="F171" t="s">
+      <c r="F171" s="1" t="s">
         <v>957</v>
       </c>
       <c r="G171" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>958</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="1" t="s">
         <v>959</v>
       </c>
       <c r="C172" t="s">
@@ -8487,21 +9003,24 @@
       <c r="D172" t="s">
         <v>961</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F172" s="1" t="s">
         <v>962</v>
       </c>
       <c r="G172" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>963</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="1" t="s">
         <v>964</v>
       </c>
       <c r="C173" t="s">
@@ -8510,21 +9029,24 @@
       <c r="D173" t="s">
         <v>966</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="F173" t="s">
+      <c r="F173" s="1" t="s">
         <v>968</v>
       </c>
       <c r="G173" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>969</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="1" t="s">
         <v>970</v>
       </c>
       <c r="C174" t="s">
@@ -8533,21 +9055,24 @@
       <c r="D174" t="s">
         <v>972</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="F174" t="s">
+      <c r="F174" s="1" t="s">
         <v>974</v>
       </c>
       <c r="G174" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>975</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="1" t="s">
         <v>976</v>
       </c>
       <c r="C175" t="s">
@@ -8556,21 +9081,24 @@
       <c r="D175" t="s">
         <v>978</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F175" s="1" t="s">
         <v>979</v>
       </c>
       <c r="G175" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>980</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="1" t="s">
         <v>981</v>
       </c>
       <c r="C176" t="s">
@@ -8579,21 +9107,24 @@
       <c r="D176" t="s">
         <v>983</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="F176" t="s">
+      <c r="F176" s="1" t="s">
         <v>985</v>
       </c>
       <c r="G176" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>986</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="1" t="s">
         <v>987</v>
       </c>
       <c r="C177" t="s">
@@ -8602,21 +9133,24 @@
       <c r="D177" t="s">
         <v>989</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="F177" t="s">
+      <c r="F177" s="1" t="s">
         <v>991</v>
       </c>
       <c r="G177" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>992</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="1" t="s">
         <v>993</v>
       </c>
       <c r="C178" t="s">
@@ -8625,21 +9159,24 @@
       <c r="D178" t="s">
         <v>995</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="F178" t="s">
+      <c r="F178" s="1" t="s">
         <v>997</v>
       </c>
       <c r="G178" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>998</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="1" t="s">
         <v>999</v>
       </c>
       <c r="C179" t="s">
@@ -8648,21 +9185,24 @@
       <c r="D179" t="s">
         <v>1001</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="F179" t="s">
+      <c r="F179" s="1" t="s">
         <v>1002</v>
       </c>
       <c r="G179" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>1003</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="C180" t="s">
@@ -8671,21 +9211,24 @@
       <c r="D180" t="s">
         <v>1006</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F180" s="1" t="s">
         <v>1007</v>
       </c>
       <c r="G180" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>1008</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="1" t="s">
         <v>1009</v>
       </c>
       <c r="C181" t="s">
@@ -8694,21 +9237,24 @@
       <c r="D181" t="s">
         <v>1011</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="F181" t="s">
+      <c r="F181" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="G181" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>1013</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="1" t="s">
         <v>1014</v>
       </c>
       <c r="C182" t="s">
@@ -8717,21 +9263,24 @@
       <c r="D182" t="s">
         <v>1016</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="F182" t="s">
+      <c r="F182" s="1" t="s">
         <v>1018</v>
       </c>
       <c r="G182" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>1019</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="1" t="s">
         <v>1020</v>
       </c>
       <c r="C183" t="s">
@@ -8740,21 +9289,24 @@
       <c r="D183" t="s">
         <v>1022</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F183" s="1" t="s">
         <v>1024</v>
       </c>
       <c r="G183" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>1025</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="1" t="s">
         <v>1026</v>
       </c>
       <c r="C184" t="s">
@@ -8763,21 +9315,24 @@
       <c r="D184" t="s">
         <v>1027</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="F184" t="s">
+      <c r="F184" s="1" t="s">
         <v>1028</v>
       </c>
       <c r="G184" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>1029</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="1" t="s">
         <v>1030</v>
       </c>
       <c r="C185" t="s">
@@ -8786,21 +9341,24 @@
       <c r="D185" t="s">
         <v>1031</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="F185" t="s">
+      <c r="F185" s="1" t="s">
         <v>1033</v>
       </c>
       <c r="G185" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>1034</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="1" t="s">
         <v>1035</v>
       </c>
       <c r="C186" t="s">
@@ -8809,21 +9367,24 @@
       <c r="D186" t="s">
         <v>1036</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F186" s="1" t="s">
         <v>1038</v>
       </c>
       <c r="G186" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>1039</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="1" t="s">
         <v>1040</v>
       </c>
       <c r="C187" t="s">
@@ -8832,21 +9393,24 @@
       <c r="D187" t="s">
         <v>1042</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="F187" t="s">
+      <c r="F187" s="1" t="s">
         <v>1044</v>
       </c>
       <c r="G187" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>1045</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="1" t="s">
         <v>1046</v>
       </c>
       <c r="C188" t="s">
@@ -8855,21 +9419,24 @@
       <c r="D188" t="s">
         <v>1048</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="F188" t="s">
+      <c r="F188" s="1" t="s">
         <v>1049</v>
       </c>
       <c r="G188" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>1050</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="1" t="s">
         <v>1051</v>
       </c>
       <c r="C189" t="s">
@@ -8878,21 +9445,24 @@
       <c r="D189" t="s">
         <v>1053</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F189" t="s">
+      <c r="F189" s="1" t="s">
         <v>1054</v>
       </c>
       <c r="G189" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>1055</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="1" t="s">
         <v>1056</v>
       </c>
       <c r="C190" t="s">
@@ -8901,21 +9471,24 @@
       <c r="D190" t="s">
         <v>1057</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F190" s="1" t="s">
         <v>1059</v>
       </c>
       <c r="G190" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>1060</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="1" t="s">
         <v>1061</v>
       </c>
       <c r="C191" t="s">
@@ -8924,21 +9497,24 @@
       <c r="D191" t="s">
         <v>1063</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F191" s="1" t="s">
         <v>1065</v>
       </c>
       <c r="G191" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>1066</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="1" t="s">
         <v>1067</v>
       </c>
       <c r="C192" t="s">
@@ -8947,21 +9523,24 @@
       <c r="D192" t="s">
         <v>1068</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F192" s="1" t="s">
         <v>1070</v>
       </c>
       <c r="G192" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>1071</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="1" t="s">
         <v>1072</v>
       </c>
       <c r="C193" t="s">
@@ -8970,21 +9549,24 @@
       <c r="D193" t="s">
         <v>1073</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F193" s="1" t="s">
         <v>1074</v>
       </c>
       <c r="G193" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>1075</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="1" t="s">
         <v>1076</v>
       </c>
       <c r="C194" t="s">
@@ -8993,21 +9575,24 @@
       <c r="D194" t="s">
         <v>1078</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="F194" t="s">
+      <c r="F194" s="1" t="s">
         <v>1080</v>
       </c>
       <c r="G194" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>1081</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="1" t="s">
         <v>1082</v>
       </c>
       <c r="C195" t="s">
@@ -9016,21 +9601,24 @@
       <c r="D195" t="s">
         <v>1083</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="F195" t="s">
+      <c r="F195" s="1" t="s">
         <v>1084</v>
       </c>
       <c r="G195" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>1085</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="C196" t="s">
@@ -9039,21 +9627,24 @@
       <c r="D196" t="s">
         <v>1088</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="F196" t="s">
+      <c r="F196" s="1" t="s">
         <v>1090</v>
       </c>
       <c r="G196" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1091</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="1" t="s">
         <v>1092</v>
       </c>
       <c r="C197" t="s">
@@ -9062,21 +9653,24 @@
       <c r="D197" t="s">
         <v>1094</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="F197" t="s">
+      <c r="F197" s="1" t="s">
         <v>1096</v>
       </c>
       <c r="G197" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>1097</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="1" t="s">
         <v>1098</v>
       </c>
       <c r="C198" t="s">
@@ -9085,21 +9679,24 @@
       <c r="D198" t="s">
         <v>1099</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="F198" t="s">
+      <c r="F198" s="1" t="s">
         <v>1100</v>
       </c>
       <c r="G198" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>1101</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="1" t="s">
         <v>1102</v>
       </c>
       <c r="C199" t="s">
@@ -9108,21 +9705,24 @@
       <c r="D199" t="s">
         <v>1104</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="F199" t="s">
+      <c r="F199" s="1" t="s">
         <v>1106</v>
       </c>
       <c r="G199" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>1107</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="1" t="s">
         <v>1108</v>
       </c>
       <c r="C200" t="s">
@@ -9131,21 +9731,24 @@
       <c r="D200" t="s">
         <v>1109</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="F200" t="s">
+      <c r="F200" s="1" t="s">
         <v>1111</v>
       </c>
       <c r="G200" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1112</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="1" t="s">
         <v>1113</v>
       </c>
       <c r="C201" t="s">
@@ -9154,21 +9757,24 @@
       <c r="D201" t="s">
         <v>1115</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="F201" t="s">
+      <c r="F201" s="1" t="s">
         <v>1117</v>
       </c>
       <c r="G201" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1118</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="1" t="s">
         <v>1119</v>
       </c>
       <c r="C202" t="s">
@@ -9177,21 +9783,24 @@
       <c r="D202" t="s">
         <v>1121</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F202" s="1" t="s">
         <v>1123</v>
       </c>
       <c r="G202" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1124</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="1" t="s">
         <v>1125</v>
       </c>
       <c r="C203" t="s">
@@ -9200,21 +9809,24 @@
       <c r="D203" t="s">
         <v>1127</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="F203" t="s">
+      <c r="F203" s="1" t="s">
         <v>1128</v>
       </c>
       <c r="G203" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>1129</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="1" t="s">
         <v>1130</v>
       </c>
       <c r="C204" t="s">
@@ -9223,21 +9835,24 @@
       <c r="D204" t="s">
         <v>1131</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="F204" t="s">
+      <c r="F204" s="1" t="s">
         <v>1133</v>
       </c>
       <c r="G204" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>1134</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="1" t="s">
         <v>1135</v>
       </c>
       <c r="C205" t="s">
@@ -9246,21 +9861,24 @@
       <c r="D205" t="s">
         <v>1137</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E205" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="F205" t="s">
+      <c r="F205" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="G205" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>1139</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="1" t="s">
         <v>1140</v>
       </c>
       <c r="C206" t="s">
@@ -9269,21 +9887,24 @@
       <c r="D206" t="s">
         <v>1141</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="F206" t="s">
+      <c r="F206" s="1" t="s">
         <v>1142</v>
       </c>
       <c r="G206" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>1143</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="C207" t="s">
@@ -9292,21 +9913,24 @@
       <c r="D207" t="s">
         <v>1146</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="F207" t="s">
+      <c r="F207" s="1" t="s">
         <v>1147</v>
       </c>
       <c r="G207" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>1148</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="1" t="s">
         <v>1149</v>
       </c>
       <c r="C208" t="s">
@@ -9315,21 +9939,24 @@
       <c r="D208" t="s">
         <v>1151</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="F208" t="s">
+      <c r="F208" s="1" t="s">
         <v>1152</v>
       </c>
       <c r="G208" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>1153</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="1" t="s">
         <v>1154</v>
       </c>
       <c r="C209" t="s">
@@ -9338,21 +9965,24 @@
       <c r="D209" t="s">
         <v>1156</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="F209" t="s">
+      <c r="F209" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="G209" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>1159</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="1" t="s">
         <v>1160</v>
       </c>
       <c r="C210" t="s">
@@ -9361,21 +9991,24 @@
       <c r="D210" t="s">
         <v>1161</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E210" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="F210" t="s">
+      <c r="F210" s="1" t="s">
         <v>1163</v>
       </c>
       <c r="G210" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>1164</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="1" t="s">
         <v>1165</v>
       </c>
       <c r="C211" t="s">
@@ -9384,21 +10017,24 @@
       <c r="D211" t="s">
         <v>1167</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E211" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="F211" t="s">
+      <c r="F211" s="1" t="s">
         <v>1168</v>
       </c>
       <c r="G211" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>1169</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="1" t="s">
         <v>1170</v>
       </c>
       <c r="C212" t="s">
@@ -9407,21 +10043,24 @@
       <c r="D212" t="s">
         <v>1172</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E212" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F212" s="1" t="s">
         <v>1173</v>
       </c>
       <c r="G212" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>1174</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="1" t="s">
         <v>1175</v>
       </c>
       <c r="C213" t="s">
@@ -9430,21 +10069,24 @@
       <c r="D213" t="s">
         <v>1177</v>
       </c>
-      <c r="E213" t="s">
+      <c r="E213" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="F213" t="s">
+      <c r="F213" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="G213" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>1179</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="1" t="s">
         <v>1180</v>
       </c>
       <c r="C214" t="s">
@@ -9453,21 +10095,24 @@
       <c r="D214" t="s">
         <v>1182</v>
       </c>
-      <c r="E214" t="s">
+      <c r="E214" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="F214" t="s">
+      <c r="F214" s="1" t="s">
         <v>1183</v>
       </c>
       <c r="G214" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>1184</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="1" t="s">
         <v>1185</v>
       </c>
       <c r="C215" t="s">
@@ -9476,21 +10121,24 @@
       <c r="D215" t="s">
         <v>1187</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E215" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="F215" t="s">
+      <c r="F215" s="1" t="s">
         <v>1189</v>
       </c>
       <c r="G215" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>1190</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="1" t="s">
         <v>1191</v>
       </c>
       <c r="C216" t="s">
@@ -9499,21 +10147,24 @@
       <c r="D216" t="s">
         <v>1193</v>
       </c>
-      <c r="E216" t="s">
+      <c r="E216" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="F216" t="s">
+      <c r="F216" s="1" t="s">
         <v>1195</v>
       </c>
       <c r="G216" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>1196</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="1" t="s">
         <v>1197</v>
       </c>
       <c r="C217" t="s">
@@ -9522,21 +10173,24 @@
       <c r="D217" t="s">
         <v>1199</v>
       </c>
-      <c r="E217" t="s">
+      <c r="E217" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="F217" t="s">
+      <c r="F217" s="1" t="s">
         <v>1201</v>
       </c>
       <c r="G217" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>1202</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="1" t="s">
         <v>1203</v>
       </c>
       <c r="C218" t="s">
@@ -9545,21 +10199,24 @@
       <c r="D218" t="s">
         <v>1205</v>
       </c>
-      <c r="E218" t="s">
+      <c r="E218" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="F218" t="s">
+      <c r="F218" s="1" t="s">
         <v>1207</v>
       </c>
       <c r="G218" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>1208</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="C219" t="s">
@@ -9568,21 +10225,24 @@
       <c r="D219" t="s">
         <v>1211</v>
       </c>
-      <c r="E219" t="s">
+      <c r="E219" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F219" s="1" t="s">
         <v>1213</v>
       </c>
       <c r="G219" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>1214</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="1" t="s">
         <v>1215</v>
       </c>
       <c r="C220" t="s">
@@ -9591,21 +10251,24 @@
       <c r="D220" t="s">
         <v>1217</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E220" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F220" s="1" t="s">
         <v>1219</v>
       </c>
       <c r="G220" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>1220</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="1" t="s">
         <v>1221</v>
       </c>
       <c r="C221" t="s">
@@ -9614,21 +10277,24 @@
       <c r="D221" t="s">
         <v>1223</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="F221" t="s">
+      <c r="F221" s="1" t="s">
         <v>1224</v>
       </c>
       <c r="G221" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>1225</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="1" t="s">
         <v>1226</v>
       </c>
       <c r="C222" t="s">
@@ -9637,21 +10303,24 @@
       <c r="D222" t="s">
         <v>1228</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E222" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="F222" t="s">
+      <c r="F222" s="1" t="s">
         <v>1229</v>
       </c>
       <c r="G222" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>1230</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="1" t="s">
         <v>1231</v>
       </c>
       <c r="C223" t="s">
@@ -9660,21 +10329,24 @@
       <c r="D223" t="s">
         <v>1233</v>
       </c>
-      <c r="E223" t="s">
+      <c r="E223" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="F223" t="s">
+      <c r="F223" s="1" t="s">
         <v>1234</v>
       </c>
       <c r="G223" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>1235</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="1" t="s">
         <v>1236</v>
       </c>
       <c r="C224" t="s">
@@ -9683,21 +10355,24 @@
       <c r="D224" t="s">
         <v>1238</v>
       </c>
-      <c r="E224" t="s">
+      <c r="E224" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F224" s="1" t="s">
         <v>1240</v>
       </c>
       <c r="G224" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>1241</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="1" t="s">
         <v>1242</v>
       </c>
       <c r="C225" t="s">
@@ -9706,21 +10381,24 @@
       <c r="D225" t="s">
         <v>1244</v>
       </c>
-      <c r="E225" t="s">
+      <c r="E225" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F225" s="1" t="s">
         <v>1245</v>
       </c>
       <c r="G225" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>1246</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="1" t="s">
         <v>1247</v>
       </c>
       <c r="C226" t="s">
@@ -9729,21 +10407,24 @@
       <c r="D226" t="s">
         <v>1249</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E226" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F226" s="1" t="s">
         <v>1251</v>
       </c>
       <c r="G226" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1252</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="1" t="s">
         <v>1253</v>
       </c>
       <c r="C227" t="s">
@@ -9752,21 +10433,24 @@
       <c r="D227" t="s">
         <v>1255</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="G227" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1258</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="1" t="s">
         <v>1259</v>
       </c>
       <c r="C228" t="s">
@@ -9775,21 +10459,24 @@
       <c r="D228" t="s">
         <v>1261</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E228" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="F228" t="s">
+      <c r="F228" s="1" t="s">
         <v>1262</v>
       </c>
       <c r="G228" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>1263</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="1" t="s">
         <v>1264</v>
       </c>
       <c r="C229" t="s">
@@ -9798,21 +10485,24 @@
       <c r="D229" t="s">
         <v>1265</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="F229" t="s">
+      <c r="F229" s="1" t="s">
         <v>1266</v>
       </c>
       <c r="G229" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>1267</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="1" t="s">
         <v>1268</v>
       </c>
       <c r="C230" t="s">
@@ -9821,21 +10511,24 @@
       <c r="D230" t="s">
         <v>1270</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E230" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="F230" t="s">
+      <c r="F230" s="1" t="s">
         <v>1272</v>
       </c>
       <c r="G230" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>1273</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="1" t="s">
         <v>1274</v>
       </c>
       <c r="C231" t="s">
@@ -9844,21 +10537,24 @@
       <c r="D231" t="s">
         <v>1275</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E231" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="F231" t="s">
+      <c r="F231" s="1" t="s">
         <v>1277</v>
       </c>
       <c r="G231" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>1278</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="1" t="s">
         <v>1279</v>
       </c>
       <c r="C232" t="s">
@@ -9867,21 +10563,24 @@
       <c r="D232" t="s">
         <v>1281</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E232" s="1" t="s">
         <v>1282</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F232" s="1" t="s">
         <v>1283</v>
       </c>
       <c r="G232" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>1284</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="1" t="s">
         <v>1285</v>
       </c>
       <c r="C233" t="s">
@@ -9890,21 +10589,24 @@
       <c r="D233" t="s">
         <v>1287</v>
       </c>
-      <c r="E233" t="s">
+      <c r="E233" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="F233" t="s">
+      <c r="F233" s="1" t="s">
         <v>1289</v>
       </c>
       <c r="G233" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>1290</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="1" t="s">
         <v>1291</v>
       </c>
       <c r="C234" t="s">
@@ -9913,21 +10615,24 @@
       <c r="D234" t="s">
         <v>1292</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E234" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="F234" t="s">
+      <c r="F234" s="1" t="s">
         <v>1293</v>
       </c>
       <c r="G234" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>1294</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="1" t="s">
         <v>1295</v>
       </c>
       <c r="C235" t="s">
@@ -9936,21 +10641,24 @@
       <c r="D235" t="s">
         <v>1297</v>
       </c>
-      <c r="E235" t="s">
+      <c r="E235" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="F235" t="s">
+      <c r="F235" s="1" t="s">
         <v>1299</v>
       </c>
       <c r="G235" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>1300</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="1" t="s">
         <v>1301</v>
       </c>
       <c r="C236" t="s">
@@ -9959,21 +10667,24 @@
       <c r="D236" t="s">
         <v>1302</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E236" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="F236" t="s">
+      <c r="F236" s="1" t="s">
         <v>1304</v>
       </c>
       <c r="G236" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>1305</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="1" t="s">
         <v>1306</v>
       </c>
       <c r="C237" t="s">
@@ -9982,21 +10693,24 @@
       <c r="D237" t="s">
         <v>1308</v>
       </c>
-      <c r="E237" t="s">
+      <c r="E237" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F237" s="1" t="s">
         <v>1310</v>
       </c>
       <c r="G237" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>1311</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="1" t="s">
         <v>1312</v>
       </c>
       <c r="C238" t="s">
@@ -10005,21 +10719,24 @@
       <c r="D238" t="s">
         <v>1314</v>
       </c>
-      <c r="E238" t="s">
+      <c r="E238" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="F238" t="s">
+      <c r="F238" s="1" t="s">
         <v>1315</v>
       </c>
       <c r="G238" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>1316</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="1" t="s">
         <v>1317</v>
       </c>
       <c r="C239" t="s">
@@ -10028,21 +10745,24 @@
       <c r="D239" t="s">
         <v>1319</v>
       </c>
-      <c r="E239" t="s">
+      <c r="E239" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F239" s="1" t="s">
         <v>1320</v>
       </c>
       <c r="G239" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>1321</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="1" t="s">
         <v>1322</v>
       </c>
       <c r="C240" t="s">
@@ -10051,21 +10771,24 @@
       <c r="D240" t="s">
         <v>1324</v>
       </c>
-      <c r="E240" t="s">
+      <c r="E240" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F240" s="1" t="s">
         <v>1326</v>
       </c>
       <c r="G240" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>1327</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="1" t="s">
         <v>1328</v>
       </c>
       <c r="C241" t="s">
@@ -10074,21 +10797,24 @@
       <c r="D241" t="s">
         <v>1330</v>
       </c>
-      <c r="E241" t="s">
+      <c r="E241" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="F241" t="s">
+      <c r="F241" s="1" t="s">
         <v>1332</v>
       </c>
       <c r="G241" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>1333</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="1" t="s">
         <v>1334</v>
       </c>
       <c r="C242" t="s">
@@ -10097,21 +10823,24 @@
       <c r="D242" t="s">
         <v>1336</v>
       </c>
-      <c r="E242" t="s">
+      <c r="E242" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F242" s="1" t="s">
         <v>1338</v>
       </c>
       <c r="G242" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>1339</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="1" t="s">
         <v>1340</v>
       </c>
       <c r="C243" t="s">
@@ -10120,21 +10849,24 @@
       <c r="D243" t="s">
         <v>1342</v>
       </c>
-      <c r="E243" t="s">
+      <c r="E243" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="F243" t="s">
+      <c r="F243" s="1" t="s">
         <v>1344</v>
       </c>
       <c r="G243" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>1345</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="1" t="s">
         <v>1346</v>
       </c>
       <c r="C244" t="s">
@@ -10143,21 +10875,24 @@
       <c r="D244" t="s">
         <v>1348</v>
       </c>
-      <c r="E244" t="s">
+      <c r="E244" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="F244" t="s">
+      <c r="F244" s="1" t="s">
         <v>1350</v>
       </c>
       <c r="G244" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1351</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="1" t="s">
         <v>1352</v>
       </c>
       <c r="C245" t="s">
@@ -10166,21 +10901,24 @@
       <c r="D245" t="s">
         <v>1354</v>
       </c>
-      <c r="E245" t="s">
+      <c r="E245" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="F245" t="s">
+      <c r="F245" s="1" t="s">
         <v>1355</v>
       </c>
       <c r="G245" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1356</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="1" t="s">
         <v>1357</v>
       </c>
       <c r="C246" t="s">
@@ -10189,21 +10927,24 @@
       <c r="D246" t="s">
         <v>1359</v>
       </c>
-      <c r="E246" t="s">
+      <c r="E246" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="F246" t="s">
+      <c r="F246" s="1" t="s">
         <v>1361</v>
       </c>
       <c r="G246" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>1362</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="1" t="s">
         <v>1363</v>
       </c>
       <c r="C247" t="s">
@@ -10212,21 +10953,24 @@
       <c r="D247" t="s">
         <v>1364</v>
       </c>
-      <c r="E247" t="s">
+      <c r="E247" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="F247" t="s">
+      <c r="F247" s="1" t="s">
         <v>1366</v>
       </c>
       <c r="G247" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>1367</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="1" t="s">
         <v>1368</v>
       </c>
       <c r="C248" t="s">
@@ -10235,21 +10979,24 @@
       <c r="D248" t="s">
         <v>1370</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E248" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="F248" t="s">
+      <c r="F248" s="1" t="s">
         <v>1372</v>
       </c>
       <c r="G248" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>1373</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="1" t="s">
         <v>1374</v>
       </c>
       <c r="C249" t="s">
@@ -10258,21 +11005,24 @@
       <c r="D249" t="s">
         <v>1376</v>
       </c>
-      <c r="E249" t="s">
+      <c r="E249" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="F249" t="s">
+      <c r="F249" s="1" t="s">
         <v>1378</v>
       </c>
       <c r="G249" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>1379</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="1" t="s">
         <v>1380</v>
       </c>
       <c r="C250" t="s">
@@ -10281,21 +11031,24 @@
       <c r="D250" t="s">
         <v>1382</v>
       </c>
-      <c r="E250" t="s">
+      <c r="E250" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="F250" t="s">
+      <c r="F250" s="1" t="s">
         <v>1384</v>
       </c>
       <c r="G250" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>1385</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="1" t="s">
         <v>1386</v>
       </c>
       <c r="C251" t="s">
@@ -10304,14 +11057,17 @@
       <c r="D251" t="s">
         <v>1388</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E251" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="F251" t="s">
+      <c r="F251" s="1" t="s">
         <v>1389</v>
       </c>
       <c r="G251" t="s">
         <v>14</v>
+      </c>
+      <c r="H251">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/rag/evaluation/Annotations-flan-t5-large.xlsx
+++ b/rag/evaluation/Annotations-flan-t5-large.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Desktop/nlp-hw1/rag/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A739418-3C34-BC49-A881-4A031DDF8A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A863584E-8D08-3949-968A-B48C6F7B9903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1391">
   <si>
     <t>query_id</t>
   </si>
@@ -4190,13 +4190,23 @@
   </si>
   <si>
     <t>Curtis Emerson LeMay</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4205,12 +4215,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4225,9 +4247,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4535,6 +4564,7 @@
   <dimension ref="A1:I251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="53.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
@@ -4595,6 +4625,9 @@
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -4621,6 +4654,9 @@
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -4647,6 +4683,9 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -4673,6 +4712,9 @@
       <c r="H5">
         <v>0</v>
       </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -4699,6 +4741,9 @@
       <c r="H6">
         <v>1</v>
       </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -4725,6 +4770,9 @@
       <c r="H7">
         <v>1</v>
       </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -4751,6 +4799,9 @@
       <c r="H8">
         <v>1</v>
       </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -4777,6 +4828,9 @@
       <c r="H9">
         <v>1</v>
       </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -4803,6 +4857,9 @@
       <c r="H10">
         <v>1</v>
       </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -4829,6 +4886,9 @@
       <c r="H11">
         <v>1</v>
       </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -4855,6 +4915,9 @@
       <c r="H12">
         <v>1</v>
       </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -4881,6 +4944,9 @@
       <c r="H13">
         <v>0</v>
       </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -4907,6 +4973,9 @@
       <c r="H14">
         <v>0</v>
       </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -4933,6 +5002,9 @@
       <c r="H15">
         <v>1</v>
       </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -4959,8 +5031,11 @@
       <c r="H16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -4985,8 +5060,11 @@
       <c r="H17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -5011,8 +5089,11 @@
       <c r="H18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>105</v>
       </c>
@@ -5037,8 +5118,11 @@
       <c r="H19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -5063,8 +5147,11 @@
       <c r="H20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -5089,8 +5176,11 @@
       <c r="H21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -5115,8 +5205,11 @@
       <c r="H22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>125</v>
       </c>
@@ -5141,8 +5234,11 @@
       <c r="H23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>130</v>
       </c>
@@ -5167,8 +5263,11 @@
       <c r="H24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>136</v>
       </c>
@@ -5193,8 +5292,11 @@
       <c r="H25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -5219,8 +5321,11 @@
       <c r="H26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>146</v>
       </c>
@@ -5245,8 +5350,11 @@
       <c r="H27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>152</v>
       </c>
@@ -5271,8 +5379,11 @@
       <c r="H28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>158</v>
       </c>
@@ -5297,8 +5408,11 @@
       <c r="H29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>163</v>
       </c>
@@ -5323,8 +5437,11 @@
       <c r="H30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -5349,8 +5466,11 @@
       <c r="H31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -5375,8 +5495,11 @@
       <c r="H32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -5401,8 +5524,11 @@
       <c r="H33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -5427,8 +5553,11 @@
       <c r="H34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -5453,8 +5582,11 @@
       <c r="H35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -5479,8 +5611,11 @@
       <c r="H36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>202</v>
       </c>
@@ -5505,8 +5640,11 @@
       <c r="H37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>206</v>
       </c>
@@ -5531,8 +5669,11 @@
       <c r="H38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>211</v>
       </c>
@@ -5557,8 +5698,11 @@
       <c r="H39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>217</v>
       </c>
@@ -5583,8 +5727,11 @@
       <c r="H40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>223</v>
       </c>
@@ -5609,8 +5756,11 @@
       <c r="H41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>229</v>
       </c>
@@ -5633,10 +5783,13 @@
         <v>14</v>
       </c>
       <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>234</v>
       </c>
@@ -5661,8 +5814,11 @@
       <c r="H43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>240</v>
       </c>
@@ -5687,8 +5843,11 @@
       <c r="H44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>245</v>
       </c>
@@ -5713,8 +5872,11 @@
       <c r="H45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>250</v>
       </c>
@@ -5739,8 +5901,11 @@
       <c r="H46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>256</v>
       </c>
@@ -5765,8 +5930,11 @@
       <c r="H47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I47" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>261</v>
       </c>
@@ -5791,8 +5959,11 @@
       <c r="H48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>267</v>
       </c>
@@ -5817,8 +5988,11 @@
       <c r="H49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>273</v>
       </c>
@@ -5843,8 +6017,11 @@
       <c r="H50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>279</v>
       </c>
@@ -5869,8 +6046,11 @@
       <c r="H51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>285</v>
       </c>
@@ -5895,8 +6075,11 @@
       <c r="H52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>291</v>
       </c>
@@ -5921,8 +6104,11 @@
       <c r="H53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>297</v>
       </c>
@@ -5947,8 +6133,11 @@
       <c r="H54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>302</v>
       </c>
@@ -5973,8 +6162,11 @@
       <c r="H55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>308</v>
       </c>
@@ -5999,8 +6191,11 @@
       <c r="H56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>314</v>
       </c>
@@ -6025,8 +6220,11 @@
       <c r="H57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>320</v>
       </c>
@@ -6051,8 +6249,11 @@
       <c r="H58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>325</v>
       </c>
@@ -6077,8 +6278,11 @@
       <c r="H59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>330</v>
       </c>
@@ -6103,8 +6307,11 @@
       <c r="H60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>335</v>
       </c>
@@ -6129,8 +6336,11 @@
       <c r="H61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>341</v>
       </c>
@@ -6155,8 +6365,11 @@
       <c r="H62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>347</v>
       </c>
@@ -6181,8 +6394,11 @@
       <c r="H63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>352</v>
       </c>
@@ -6207,8 +6423,11 @@
       <c r="H64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="96" x14ac:dyDescent="0.2">
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>358</v>
       </c>
@@ -6233,8 +6452,11 @@
       <c r="H65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>363</v>
       </c>
@@ -6259,8 +6481,11 @@
       <c r="H66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>369</v>
       </c>
@@ -6285,8 +6510,11 @@
       <c r="H67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>374</v>
       </c>
@@ -6311,8 +6539,11 @@
       <c r="H68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>379</v>
       </c>
@@ -6337,8 +6568,11 @@
       <c r="H69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>385</v>
       </c>
@@ -6363,8 +6597,11 @@
       <c r="H70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>391</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="H71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>397</v>
       </c>
@@ -6415,8 +6655,11 @@
       <c r="H72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I72" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>403</v>
       </c>
@@ -6441,8 +6684,11 @@
       <c r="H73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>409</v>
       </c>
@@ -6467,8 +6713,11 @@
       <c r="H74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>415</v>
       </c>
@@ -6493,8 +6742,11 @@
       <c r="H75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>421</v>
       </c>
@@ -6519,8 +6771,11 @@
       <c r="H76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>426</v>
       </c>
@@ -6545,8 +6800,11 @@
       <c r="H77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="112" x14ac:dyDescent="0.2">
+      <c r="I77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="112" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>431</v>
       </c>
@@ -6571,8 +6829,11 @@
       <c r="H78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>437</v>
       </c>
@@ -6597,8 +6858,11 @@
       <c r="H79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>443</v>
       </c>
@@ -6623,8 +6887,11 @@
       <c r="H80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>449</v>
       </c>
@@ -6649,8 +6916,11 @@
       <c r="H81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I81" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>454</v>
       </c>
@@ -6675,8 +6945,11 @@
       <c r="H82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>460</v>
       </c>
@@ -6701,8 +6974,11 @@
       <c r="H83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>466</v>
       </c>
@@ -6727,8 +7003,11 @@
       <c r="H84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>472</v>
       </c>
@@ -6753,8 +7032,11 @@
       <c r="H85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>477</v>
       </c>
@@ -6779,8 +7061,11 @@
       <c r="H86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>483</v>
       </c>
@@ -6805,8 +7090,11 @@
       <c r="H87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I87" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>488</v>
       </c>
@@ -6831,8 +7119,11 @@
       <c r="H88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>494</v>
       </c>
@@ -6857,8 +7148,11 @@
       <c r="H89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>499</v>
       </c>
@@ -6883,8 +7177,11 @@
       <c r="H90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>505</v>
       </c>
@@ -6909,8 +7206,11 @@
       <c r="H91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>511</v>
       </c>
@@ -6933,10 +7233,13 @@
         <v>14</v>
       </c>
       <c r="H92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>517</v>
       </c>
@@ -6961,8 +7264,11 @@
       <c r="H93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>523</v>
       </c>
@@ -6987,8 +7293,11 @@
       <c r="H94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I94" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>529</v>
       </c>
@@ -7013,8 +7322,11 @@
       <c r="H95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I95" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>535</v>
       </c>
@@ -7039,8 +7351,11 @@
       <c r="H96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I96" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>540</v>
       </c>
@@ -7065,8 +7380,11 @@
       <c r="H97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I97" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>546</v>
       </c>
@@ -7089,10 +7407,13 @@
         <v>14</v>
       </c>
       <c r="H98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>552</v>
       </c>
@@ -7117,8 +7438,11 @@
       <c r="H99">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I99" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>558</v>
       </c>
@@ -7143,8 +7467,11 @@
       <c r="H100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>564</v>
       </c>
@@ -7169,8 +7496,11 @@
       <c r="H101">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I101" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>569</v>
       </c>
@@ -7195,8 +7525,11 @@
       <c r="H102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>575</v>
       </c>
@@ -7221,8 +7554,11 @@
       <c r="H103">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>581</v>
       </c>
@@ -7247,8 +7583,11 @@
       <c r="H104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>586</v>
       </c>
@@ -7273,8 +7612,11 @@
       <c r="H105">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I105" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>590</v>
       </c>
@@ -7299,8 +7641,11 @@
       <c r="H106">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I106" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>596</v>
       </c>
@@ -7325,8 +7670,11 @@
       <c r="H107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>602</v>
       </c>
@@ -7351,8 +7699,11 @@
       <c r="H108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" ht="112" x14ac:dyDescent="0.2">
+      <c r="I108" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="112" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>607</v>
       </c>
@@ -7377,8 +7728,11 @@
       <c r="H109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>613</v>
       </c>
@@ -7403,8 +7757,11 @@
       <c r="H110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I110" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>618</v>
       </c>
@@ -7429,8 +7786,11 @@
       <c r="H111">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I111" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>623</v>
       </c>
@@ -7455,8 +7815,11 @@
       <c r="H112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>629</v>
       </c>
@@ -7481,8 +7844,11 @@
       <c r="H113">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I113" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>633</v>
       </c>
@@ -7507,8 +7873,11 @@
       <c r="H114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I114" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>638</v>
       </c>
@@ -7533,8 +7902,11 @@
       <c r="H115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>644</v>
       </c>
@@ -7559,8 +7931,11 @@
       <c r="H116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>650</v>
       </c>
@@ -7585,8 +7960,11 @@
       <c r="H117">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I117" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>656</v>
       </c>
@@ -7611,8 +7989,11 @@
       <c r="H118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I118" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>662</v>
       </c>
@@ -7637,8 +8018,11 @@
       <c r="H119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>668</v>
       </c>
@@ -7663,8 +8047,11 @@
       <c r="H120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I120" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>673</v>
       </c>
@@ -7689,8 +8076,11 @@
       <c r="H121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I121" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>679</v>
       </c>
@@ -7715,8 +8105,11 @@
       <c r="H122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I122" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>684</v>
       </c>
@@ -7741,8 +8134,11 @@
       <c r="H123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I123" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>690</v>
       </c>
@@ -7767,8 +8163,11 @@
       <c r="H124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I124" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>696</v>
       </c>
@@ -7793,8 +8192,11 @@
       <c r="H125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I125" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>702</v>
       </c>
@@ -7819,8 +8221,11 @@
       <c r="H126">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I126" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>707</v>
       </c>
@@ -7845,8 +8250,11 @@
       <c r="H127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I127" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>713</v>
       </c>
@@ -7871,8 +8279,11 @@
       <c r="H128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I128" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>719</v>
       </c>
@@ -7897,8 +8308,11 @@
       <c r="H129">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="I129" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>723</v>
       </c>
@@ -7923,8 +8337,11 @@
       <c r="H130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I130" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>729</v>
       </c>
@@ -7949,8 +8366,11 @@
       <c r="H131">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I131" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>735</v>
       </c>
@@ -7975,8 +8395,11 @@
       <c r="H132">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I132" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>741</v>
       </c>
@@ -8001,8 +8424,11 @@
       <c r="H133">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I133" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>747</v>
       </c>
@@ -8027,8 +8453,11 @@
       <c r="H134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I134" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>753</v>
       </c>
@@ -8053,8 +8482,11 @@
       <c r="H135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I135" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>758</v>
       </c>
@@ -8079,8 +8511,11 @@
       <c r="H136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I136" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>764</v>
       </c>
@@ -8105,8 +8540,11 @@
       <c r="H137">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" ht="96" x14ac:dyDescent="0.2">
+      <c r="I137" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>770</v>
       </c>
@@ -8131,8 +8569,11 @@
       <c r="H138">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I138" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>776</v>
       </c>
@@ -8157,8 +8598,11 @@
       <c r="H139">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>781</v>
       </c>
@@ -8183,8 +8627,11 @@
       <c r="H140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I140" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>787</v>
       </c>
@@ -8209,8 +8656,11 @@
       <c r="H141">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I141" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>792</v>
       </c>
@@ -8235,8 +8685,11 @@
       <c r="H142">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I142" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>796</v>
       </c>
@@ -8261,8 +8714,11 @@
       <c r="H143">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I143" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>802</v>
       </c>
@@ -8287,8 +8743,11 @@
       <c r="H144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I144" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>808</v>
       </c>
@@ -8313,8 +8772,11 @@
       <c r="H145">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I145" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>814</v>
       </c>
@@ -8339,8 +8801,11 @@
       <c r="H146">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I146" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>820</v>
       </c>
@@ -8365,8 +8830,11 @@
       <c r="H147">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I147" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>825</v>
       </c>
@@ -8391,8 +8859,11 @@
       <c r="H148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I148" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>831</v>
       </c>
@@ -8417,8 +8888,11 @@
       <c r="H149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I149" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>837</v>
       </c>
@@ -8443,8 +8917,11 @@
       <c r="H150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I150" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>843</v>
       </c>
@@ -8469,8 +8946,11 @@
       <c r="H151">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I151" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>849</v>
       </c>
@@ -8495,8 +8975,11 @@
       <c r="H152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I152" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>855</v>
       </c>
@@ -8521,8 +9004,11 @@
       <c r="H153">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I153" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>860</v>
       </c>
@@ -8547,8 +9033,11 @@
       <c r="H154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I154" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>866</v>
       </c>
@@ -8573,8 +9062,11 @@
       <c r="H155">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I155" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>871</v>
       </c>
@@ -8599,8 +9091,11 @@
       <c r="H156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I156" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>877</v>
       </c>
@@ -8625,8 +9120,11 @@
       <c r="H157">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I157" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>881</v>
       </c>
@@ -8651,8 +9149,11 @@
       <c r="H158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I158" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>886</v>
       </c>
@@ -8677,8 +9178,11 @@
       <c r="H159">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I159" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>891</v>
       </c>
@@ -8703,8 +9207,11 @@
       <c r="H160">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I160" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>896</v>
       </c>
@@ -8729,8 +9236,11 @@
       <c r="H161">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I161" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>902</v>
       </c>
@@ -8755,8 +9265,11 @@
       <c r="H162">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I162" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>907</v>
       </c>
@@ -8781,8 +9294,11 @@
       <c r="H163">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I163" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>913</v>
       </c>
@@ -8807,8 +9323,11 @@
       <c r="H164">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I164" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>919</v>
       </c>
@@ -8833,8 +9352,11 @@
       <c r="H165">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I165" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>923</v>
       </c>
@@ -8859,8 +9381,11 @@
       <c r="H166">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I166" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>929</v>
       </c>
@@ -8885,8 +9410,11 @@
       <c r="H167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I167" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>935</v>
       </c>
@@ -8911,8 +9439,11 @@
       <c r="H168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I168" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>941</v>
       </c>
@@ -8937,8 +9468,11 @@
       <c r="H169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I169" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>947</v>
       </c>
@@ -8963,8 +9497,11 @@
       <c r="H170">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I170" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>952</v>
       </c>
@@ -8989,8 +9526,11 @@
       <c r="H171">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I171" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>958</v>
       </c>
@@ -9015,8 +9555,11 @@
       <c r="H172">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" ht="96" x14ac:dyDescent="0.2">
+      <c r="I172" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="96" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>963</v>
       </c>
@@ -9041,8 +9584,11 @@
       <c r="H173">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I173" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>969</v>
       </c>
@@ -9067,8 +9613,11 @@
       <c r="H174">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I174" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>975</v>
       </c>
@@ -9093,8 +9642,11 @@
       <c r="H175">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I175" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>980</v>
       </c>
@@ -9119,8 +9671,11 @@
       <c r="H176">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="I176" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>986</v>
       </c>
@@ -9145,8 +9700,11 @@
       <c r="H177">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I177" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>992</v>
       </c>
@@ -9171,8 +9729,11 @@
       <c r="H178">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I178" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>998</v>
       </c>
@@ -9197,8 +9758,11 @@
       <c r="H179">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I179" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>1003</v>
       </c>
@@ -9223,8 +9787,11 @@
       <c r="H180">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I180" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>1008</v>
       </c>
@@ -9249,8 +9816,11 @@
       <c r="H181">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I181" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>1013</v>
       </c>
@@ -9275,8 +9845,11 @@
       <c r="H182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I182" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>1019</v>
       </c>
@@ -9301,8 +9874,11 @@
       <c r="H183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I183" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>1025</v>
       </c>
@@ -9327,8 +9903,11 @@
       <c r="H184">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I184" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>1029</v>
       </c>
@@ -9351,10 +9930,13 @@
         <v>14</v>
       </c>
       <c r="H185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I185" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>1034</v>
       </c>
@@ -9379,8 +9961,11 @@
       <c r="H186">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I186" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>1039</v>
       </c>
@@ -9405,8 +9990,11 @@
       <c r="H187">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I187" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>1045</v>
       </c>
@@ -9431,8 +10019,11 @@
       <c r="H188">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I188" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>1050</v>
       </c>
@@ -9457,8 +10048,11 @@
       <c r="H189">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I189" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>1055</v>
       </c>
@@ -9483,8 +10077,11 @@
       <c r="H190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I190" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>1060</v>
       </c>
@@ -9509,8 +10106,11 @@
       <c r="H191">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I191" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>1066</v>
       </c>
@@ -9535,8 +10135,11 @@
       <c r="H192">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I192" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>1071</v>
       </c>
@@ -9561,8 +10164,11 @@
       <c r="H193">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I193" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>1075</v>
       </c>
@@ -9587,8 +10193,11 @@
       <c r="H194">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I194" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>1081</v>
       </c>
@@ -9613,8 +10222,11 @@
       <c r="H195">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I195" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>1085</v>
       </c>
@@ -9639,8 +10251,11 @@
       <c r="H196">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I196" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1091</v>
       </c>
@@ -9665,8 +10280,11 @@
       <c r="H197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I197" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>1097</v>
       </c>
@@ -9691,8 +10309,11 @@
       <c r="H198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I198" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>1101</v>
       </c>
@@ -9717,8 +10338,11 @@
       <c r="H199">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I199" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>1107</v>
       </c>
@@ -9743,8 +10367,11 @@
       <c r="H200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I200" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>1112</v>
       </c>
@@ -9769,8 +10396,11 @@
       <c r="H201">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I201" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1118</v>
       </c>
@@ -9795,8 +10425,11 @@
       <c r="H202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I202" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1124</v>
       </c>
@@ -9821,8 +10454,11 @@
       <c r="H203">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I203" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>1129</v>
       </c>
@@ -9847,8 +10483,11 @@
       <c r="H204">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I204" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>1134</v>
       </c>
@@ -9873,8 +10512,11 @@
       <c r="H205">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I205" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>1139</v>
       </c>
@@ -9899,8 +10541,11 @@
       <c r="H206">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I206" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>1143</v>
       </c>
@@ -9925,8 +10570,11 @@
       <c r="H207">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I207" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>1148</v>
       </c>
@@ -9951,8 +10599,11 @@
       <c r="H208">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="I208" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="80" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>1153</v>
       </c>
@@ -9977,8 +10628,11 @@
       <c r="H209">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I209" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>1159</v>
       </c>
@@ -10003,8 +10657,11 @@
       <c r="H210">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I210" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>1164</v>
       </c>
@@ -10029,8 +10686,11 @@
       <c r="H211">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I211" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>1169</v>
       </c>
@@ -10055,8 +10715,11 @@
       <c r="H212">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I212" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>1174</v>
       </c>
@@ -10081,8 +10744,11 @@
       <c r="H213">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I213" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>1179</v>
       </c>
@@ -10107,8 +10773,11 @@
       <c r="H214">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I214" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>1184</v>
       </c>
@@ -10133,8 +10802,11 @@
       <c r="H215">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I215" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>1190</v>
       </c>
@@ -10159,8 +10831,11 @@
       <c r="H216">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I216" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>1196</v>
       </c>
@@ -10185,8 +10860,11 @@
       <c r="H217">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I217" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>1202</v>
       </c>
@@ -10211,8 +10889,11 @@
       <c r="H218">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I218" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>1208</v>
       </c>
@@ -10237,8 +10918,11 @@
       <c r="H219">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I219" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>1214</v>
       </c>
@@ -10263,8 +10947,11 @@
       <c r="H220">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I220" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>1220</v>
       </c>
@@ -10289,8 +10976,11 @@
       <c r="H221">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I221" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>1225</v>
       </c>
@@ -10315,8 +11005,11 @@
       <c r="H222">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I222" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>1230</v>
       </c>
@@ -10341,8 +11034,11 @@
       <c r="H223">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I223" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>1235</v>
       </c>
@@ -10367,8 +11063,11 @@
       <c r="H224">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I224" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>1241</v>
       </c>
@@ -10393,8 +11092,11 @@
       <c r="H225">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I225" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>1246</v>
       </c>
@@ -10419,8 +11121,11 @@
       <c r="H226">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1252</v>
       </c>
@@ -10445,8 +11150,11 @@
       <c r="H227">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I227" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1258</v>
       </c>
@@ -10471,8 +11179,11 @@
       <c r="H228">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I228" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>1263</v>
       </c>
@@ -10497,8 +11208,11 @@
       <c r="H229">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I229" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>1267</v>
       </c>
@@ -10523,8 +11237,11 @@
       <c r="H230">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I230" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>1273</v>
       </c>
@@ -10549,8 +11266,11 @@
       <c r="H231">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I231" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>1278</v>
       </c>
@@ -10575,8 +11295,11 @@
       <c r="H232">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I232" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>1284</v>
       </c>
@@ -10601,8 +11324,11 @@
       <c r="H233">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I233" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>1290</v>
       </c>
@@ -10627,8 +11353,11 @@
       <c r="H234">
         <v>1</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I234" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>1294</v>
       </c>
@@ -10653,34 +11382,40 @@
       <c r="H235">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A236" t="s">
+      <c r="I235" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A236" s="5" t="s">
         <v>1300</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B236" s="6" t="s">
         <v>1301</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="D236" t="s">
+      <c r="D236" s="5" t="s">
         <v>1302</v>
       </c>
-      <c r="E236" s="1" t="s">
+      <c r="E236" s="6" t="s">
         <v>1303</v>
       </c>
-      <c r="F236" s="1" t="s">
+      <c r="F236" s="6" t="s">
         <v>1304</v>
       </c>
-      <c r="G236" t="s">
+      <c r="G236" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="H236" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I236" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>1305</v>
       </c>
@@ -10705,8 +11440,11 @@
       <c r="H237">
         <v>1</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I237" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>1311</v>
       </c>
@@ -10731,8 +11469,11 @@
       <c r="H238">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I238" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>1316</v>
       </c>
@@ -10757,8 +11498,11 @@
       <c r="H239">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I239" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>1321</v>
       </c>
@@ -10783,8 +11527,11 @@
       <c r="H240">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I240" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>1327</v>
       </c>
@@ -10809,8 +11556,11 @@
       <c r="H241">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I241" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>1333</v>
       </c>
@@ -10835,8 +11585,11 @@
       <c r="H242">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="I242" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>1339</v>
       </c>
@@ -10861,8 +11614,11 @@
       <c r="H243">
         <v>1</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I243" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>1345</v>
       </c>
@@ -10887,8 +11643,11 @@
       <c r="H244">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I244" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1351</v>
       </c>
@@ -10913,8 +11672,11 @@
       <c r="H245">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I245" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1356</v>
       </c>
@@ -10939,8 +11701,11 @@
       <c r="H246">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I246" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>1362</v>
       </c>
@@ -10965,8 +11730,11 @@
       <c r="H247">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="I247" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="48" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>1367</v>
       </c>
@@ -10989,10 +11757,13 @@
         <v>14</v>
       </c>
       <c r="H248">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I248" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>1373</v>
       </c>
@@ -11017,8 +11788,11 @@
       <c r="H249">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I249" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>1379</v>
       </c>
@@ -11043,8 +11817,11 @@
       <c r="H250">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I250" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>1385</v>
       </c>
@@ -11067,6 +11844,9 @@
         <v>14</v>
       </c>
       <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251" s="2">
         <v>1</v>
       </c>
     </row>

--- a/rag/evaluation/Annotations-flan-t5-large.xlsx
+++ b/rag/evaluation/Annotations-flan-t5-large.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Desktop/nlp-hw1/rag/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A863584E-8D08-3949-968A-B48C6F7B9903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1656DD9B-9D76-C24B-AFA0-8139C88578F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jugements" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1390">
   <si>
     <t>query_id</t>
   </si>
@@ -4190,9 +4203,6 @@
   </si>
   <si>
     <t>Curtis Emerson LeMay</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
 </sst>
 </file>
@@ -4215,24 +4225,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4253,12 +4251,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11266,7 +11264,7 @@
       <c r="H231">
         <v>1</v>
       </c>
-      <c r="I231" s="4">
+      <c r="I231" s="3">
         <v>1</v>
       </c>
     </row>
@@ -11358,60 +11356,60 @@
       </c>
     </row>
     <row r="235" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A235" t="s">
+      <c r="A235" s="4" t="s">
         <v>1294</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B235" s="5" t="s">
         <v>1295</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="4" t="s">
         <v>1296</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D235" s="4" t="s">
         <v>1297</v>
       </c>
-      <c r="E235" s="1" t="s">
+      <c r="E235" s="5" t="s">
         <v>1298</v>
       </c>
-      <c r="F235" s="1" t="s">
+      <c r="F235" s="5" t="s">
         <v>1299</v>
       </c>
-      <c r="G235" t="s">
+      <c r="G235" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H235">
-        <v>1</v>
-      </c>
-      <c r="I235" s="2">
+      <c r="H235" s="4">
+        <v>1</v>
+      </c>
+      <c r="I235" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A236" s="5" t="s">
+      <c r="A236" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="B236" s="6" t="s">
+      <c r="B236" s="5" t="s">
         <v>1301</v>
       </c>
-      <c r="C236" s="5" t="s">
+      <c r="C236" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="D236" s="5" t="s">
+      <c r="D236" s="4" t="s">
         <v>1302</v>
       </c>
-      <c r="E236" s="6" t="s">
+      <c r="E236" s="5" t="s">
         <v>1303</v>
       </c>
-      <c r="F236" s="6" t="s">
+      <c r="F236" s="5" t="s">
         <v>1304</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H236" s="5" t="s">
-        <v>1390</v>
-      </c>
-      <c r="I236" s="3">
+      <c r="H236" s="4">
+        <v>1</v>
+      </c>
+      <c r="I236" s="6">
         <v>1</v>
       </c>
     </row>
